--- a/Alzheimer's dataset.xlsx
+++ b/Alzheimer's dataset.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="22188" windowHeight="9324"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="65">
   <si>
     <t>Drug_Name</t>
   </si>
@@ -47,9 +47,6 @@
   </si>
   <si>
     <t>MeSH_ID</t>
-  </si>
-  <si>
-    <t>Label</t>
   </si>
   <si>
     <t>Prediction</t>
@@ -1041,7 +1038,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1063,9 +1060,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1075,16 +1069,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1418,7 +1406,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="浅色系标题行表格样式_0af9f8" count="10" xr9:uid="{38086131-63CA-4327-AAC6-77571AE50EDE}">
+    <tableStyle name="浅色系标题行表格样式_0af9f8" count="10" xr9:uid="{B26B8AD1-96A8-4346-8C6C-0CDA233E6D27}">
       <tableStyleElement type="wholeTable" dxfId="9"/>
       <tableStyleElement type="headerRow" dxfId="8"/>
       <tableStyleElement type="totalRow" dxfId="7"/>
@@ -1689,20 +1677,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="21.5083333333333" customWidth="1"/>
-    <col min="2" max="2" width="16.3416666666667" customWidth="1"/>
-    <col min="3" max="3" width="15.5083333333333" customWidth="1"/>
-    <col min="4" max="4" width="14.3416666666667" customWidth="1"/>
-    <col min="5" max="5" width="23.175" customWidth="1"/>
-    <col min="6" max="6" width="13.0083333333333" customWidth="1"/>
-    <col min="7" max="7" width="9.675" customWidth="1"/>
-    <col min="8" max="8" width="14.0083333333333" customWidth="1"/>
+    <col min="1" max="1" width="21.5092592592593" customWidth="1"/>
+    <col min="2" max="2" width="16.3425925925926" customWidth="1"/>
+    <col min="3" max="3" width="15.5092592592593" customWidth="1"/>
+    <col min="4" max="4" width="14.3425925925926" customWidth="1"/>
+    <col min="5" max="5" width="23.1759259259259" customWidth="1"/>
+    <col min="6" max="6" width="13.0092592592593" customWidth="1"/>
+    <col min="7" max="7" width="14.0092592592593" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
+    <row r="1" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1721,556 +1708,490 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:7">
+      <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>13</v>
       </c>
       <c r="G2" s="7">
         <v>1</v>
       </c>
-      <c r="H2" s="8">
+    </row>
+    <row r="3" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:7">
+      <c r="A3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A3" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="10" t="s">
+    <row r="4" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:7">
+      <c r="A4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="B4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="11">
+      <c r="G4" s="10">
         <v>1</v>
       </c>
-      <c r="H3" s="12">
+    </row>
+    <row r="5" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:7">
+      <c r="A5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A4" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="10" t="s">
+    <row r="6" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:7">
+      <c r="A6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:7">
+      <c r="A7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:7">
+      <c r="A8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:7">
+      <c r="A9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:7">
+      <c r="A10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:7">
+      <c r="A11" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:7">
+      <c r="A12" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:7">
+      <c r="A13" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E13" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="F13" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="11">
+      <c r="G13" s="10">
         <v>1</v>
       </c>
-      <c r="H4" s="12">
+    </row>
+    <row r="14" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:7">
+      <c r="A14" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="10" t="s">
+    <row r="15" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:7">
+      <c r="A15" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="F15" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="11">
+      <c r="G15" s="10">
         <v>1</v>
       </c>
-      <c r="H5" s="12">
+    </row>
+    <row r="16" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:7">
+      <c r="A16" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A6" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="10" t="s">
+    <row r="17" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:7">
+      <c r="A17" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="11">
+      <c r="G17" s="10">
         <v>1</v>
       </c>
-      <c r="H6" s="12">
+    </row>
+    <row r="18" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:7">
+      <c r="A18" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A7" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="10" t="s">
+    <row r="19" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:7">
+      <c r="A19" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="11">
+      <c r="G19" s="10">
         <v>1</v>
       </c>
-      <c r="H7" s="12">
+    </row>
+    <row r="20" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:7">
+      <c r="A20" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A8" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="10" t="s">
+    <row r="21" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:7">
+      <c r="A21" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="11">
+      <c r="G21" s="10">
         <v>1</v>
       </c>
-      <c r="H8" s="12">
-        <v>1</v>
-      </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A9" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="10" t="s">
+    <row r="22" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:7">
+      <c r="A22" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="11">
-        <v>1</v>
-      </c>
-      <c r="H9" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A10" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="11">
-        <v>1</v>
-      </c>
-      <c r="H10" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A11" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="11">
-        <v>1</v>
-      </c>
-      <c r="H11" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A12" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="11">
-        <v>1</v>
-      </c>
-      <c r="H12" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="11">
-        <v>0</v>
-      </c>
-      <c r="H13" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A14" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="11">
-        <v>0</v>
-      </c>
-      <c r="H14" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A15" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="11">
-        <v>0</v>
-      </c>
-      <c r="H15" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A16" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="11">
-        <v>0</v>
-      </c>
-      <c r="H16" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A17" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="11">
-        <v>0</v>
-      </c>
-      <c r="H17" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A18" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="11">
-        <v>0</v>
-      </c>
-      <c r="H18" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A19" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="11">
-        <v>0</v>
-      </c>
-      <c r="H19" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A20" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="11">
-        <v>0</v>
-      </c>
-      <c r="H20" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A21" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="11">
-        <v>0</v>
-      </c>
-      <c r="H21" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A22" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="15">
-        <v>0</v>
-      </c>
-      <c r="H22" s="16">
+      <c r="G22" s="13">
         <v>1</v>
       </c>
     </row>
@@ -2285,7 +2206,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2297,7 +2218,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
